--- a/artfynd/A 16182-2026 artfynd.xlsx
+++ b/artfynd/A 16182-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113422949</v>
+        <v>67728589</v>
       </c>
       <c r="B2" t="n">
-        <v>56115</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100077</v>
+        <v>426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Axmar bruk, Hls</t>
+          <t>ca 200 m norr om Axmar bruk, öster om masten, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615626</v>
+        <v>615681</v>
       </c>
       <c r="R2" t="n">
-        <v>6770686</v>
+        <v>6770647</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -734,32 +727,27 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Söderhamn</t>
+          <t>Gävle</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Hälsingland</t>
+          <t>Gästrikland</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Skog</t>
+          <t>Hamrånge</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2017-09-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1 st utter. Utter-ränna i snö invid bäck och översvämningsområde.</t>
+          <t>2017-09-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,21 +756,336 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Monica Svensson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Monica Svensson, Alf Bjarne Roland Pallin, Magnus Andersson, Laila Bissman, Anders Olsson, Lotta Delin</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsgruppen, Naturskyddsföreningen Gävleborg</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>67728588</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90662</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1594</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svartfjällig musseron</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tricholoma atrosquamosum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sacc.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ca 200 m norr om Axmar bruk, öster om masten, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>615681</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6770647</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hamrånge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2017-09-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2017-09-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Monica Svensson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Monica Svensson, Alf Bjarne Roland Pallin, Magnus Andersson, Laila Bissman, Anders Olsson, Lotta Delin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsgruppen, Naturskyddsföreningen Gävleborg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>67728581</v>
+      </c>
+      <c r="B4" t="n">
+        <v>87412</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ca 200 m norr om Axmar bruk, öster om masten, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>615681</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6770647</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hamrånge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-09-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-09-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Monica Svensson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Monica Svensson, Alf Bjarne Roland Pallin, Magnus Andersson, Laila Bissman, Anders Olsson, Lotta Delin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skogsgruppen, Naturskyddsföreningen Gävleborg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113422949</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56766</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Axmar bruk, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>615626</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6770686</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-11-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-11-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 st utter. Utter-ränna i snö invid bäck och översvämningsområde.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Göran Vesslén</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Göran Vesslén</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16182-2026 artfynd.xlsx
+++ b/artfynd/A 16182-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
           <t>Skogsgruppen, Naturskyddsföreningen Gävleborg</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67728589</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Skogsgruppen, Naturskyddsföreningen Gävleborg</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67728588</t>
         </is>
       </c>
     </row>
@@ -980,6 +995,11 @@
           <t>Skogsgruppen, Naturskyddsföreningen Gävleborg</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67728581</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,8 +1106,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113422949</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>